--- a/area_ismael.xlsx
+++ b/area_ismael.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d9c7f5cb995c5f2/Documentos/ProjetoPython/AfirmaSUS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A915459A-A95D-4D3A-9069-6AF18F04FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{A915459A-A95D-4D3A-9069-6AF18F04FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A9631B6-35F9-49DD-A21E-2153DD54EA16}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B2BFE4F-5340-43B0-ABB5-BC28A4CD0924}"/>
   </bookViews>
   <sheets>
     <sheet name="area_ismael" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="71">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -28,27 +41,12 @@
     <t>Nome</t>
   </si>
   <si>
-    <t>Nome da Rua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIA </t>
-  </si>
-  <si>
     <t>Turno</t>
   </si>
   <si>
-    <t>Horario:</t>
-  </si>
-  <si>
-    <t>Topico a ser abordado</t>
-  </si>
-  <si>
     <t xml:space="preserve">AntÃ´nia </t>
   </si>
   <si>
-    <t>Rio Amazonas</t>
-  </si>
-  <si>
     <t>Sexta</t>
   </si>
   <si>
@@ -61,9 +59,6 @@
     <t>Marlene</t>
   </si>
   <si>
-    <t>nenhum</t>
-  </si>
-  <si>
     <t>Quinta</t>
   </si>
   <si>
@@ -88,9 +83,6 @@
     <t xml:space="preserve">Denise </t>
   </si>
   <si>
-    <t>Rua Arquivista jonathas carecas</t>
-  </si>
-  <si>
     <t xml:space="preserve">JosÃ© Marcos </t>
   </si>
   <si>
@@ -109,9 +101,6 @@
     <t>Domingo</t>
   </si>
   <si>
-    <t>Tarde, Noite</t>
-  </si>
-  <si>
     <t>Saúde Mental</t>
   </si>
   <si>
@@ -145,12 +134,6 @@
     <t>Indiara</t>
   </si>
   <si>
-    <t>Sem dia definido</t>
-  </si>
-  <si>
-    <t>Sem turno definido</t>
-  </si>
-  <si>
     <t>Não Especificado</t>
   </si>
   <si>
@@ -211,9 +194,6 @@
     <t>Layane</t>
   </si>
   <si>
-    <t>Rua Liberdade</t>
-  </si>
-  <si>
     <t>vitor</t>
   </si>
   <si>
@@ -223,9 +203,6 @@
     <t>josÃ© da penha</t>
   </si>
   <si>
-    <t>Manhã, Tarde</t>
-  </si>
-  <si>
     <t>Hipertensão</t>
   </si>
   <si>
@@ -242,6 +219,33 @@
   </si>
   <si>
     <t>Atividades Contra Vícios</t>
+  </si>
+  <si>
+    <t>Rua</t>
+  </si>
+  <si>
+    <t>Dia</t>
+  </si>
+  <si>
+    <t>Horário</t>
+  </si>
+  <si>
+    <t>Tópico</t>
+  </si>
+  <si>
+    <t>Qualquer Dia</t>
+  </si>
+  <si>
+    <t>RIO AMAZONAS</t>
+  </si>
+  <si>
+    <t>NENHUM</t>
+  </si>
+  <si>
+    <t>RUA ARQUIVISTA JONATHAS CARECAS</t>
+  </si>
+  <si>
+    <t>RUA LIBERDADE</t>
   </si>
 </sst>
 </file>
@@ -1106,6 +1110,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB1F0A3-556D-4086-8F57-69444587D9FC}">
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1115,19 +1128,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1135,22 +1148,22 @@
         <v>46276.329861111109</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
         <v>0.20833333333333334</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1158,22 +1171,22 @@
         <v>46276.331944444442</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1181,22 +1194,22 @@
         <v>46276.34652777778</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
         <v>0.375</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1204,22 +1217,22 @@
         <v>46276.356944444444</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1227,19 +1240,22 @@
         <v>46276.359722222223</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
       </c>
       <c r="F6" s="2">
         <v>0.54166666666666663</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1247,22 +1263,22 @@
         <v>46276.370833333334</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2">
         <v>0.39583333333333331</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1270,22 +1286,22 @@
         <v>46276.38958333333</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2">
         <v>0.375</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1293,22 +1309,22 @@
         <v>46276.55972222222</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
         <v>0.66666666666666663</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1316,22 +1332,22 @@
         <v>46276.560416666667</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2">
         <v>0.66666666666666663</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1339,22 +1355,22 @@
         <v>46279.36041666667</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1362,22 +1378,22 @@
         <v>46279.364583333336</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F12" s="2">
         <v>0.75</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1385,16 +1401,19 @@
         <v>46280.352777777778</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1402,22 +1421,22 @@
         <v>46280.354166666664</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2">
         <v>0.375</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1425,22 +1444,22 @@
         <v>46280.356249999997</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1448,22 +1467,22 @@
         <v>46280.361805555556</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2">
         <v>0.66666666666666663</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1471,22 +1490,22 @@
         <v>46280.374305555553</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2">
         <v>0.375</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1494,22 +1513,22 @@
         <v>46280.384722222225</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1517,22 +1536,22 @@
         <v>46280.556250000001</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1540,22 +1559,22 @@
         <v>46280.56527777778</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1563,22 +1582,22 @@
         <v>46280.570138888892</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1586,22 +1605,22 @@
         <v>46281.566666666666</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1609,22 +1628,22 @@
         <v>46281.570138888892</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1632,22 +1651,22 @@
         <v>46286.379861111112</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1655,22 +1674,22 @@
         <v>46287.401388888888</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F25" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1678,22 +1697,22 @@
         <v>46287.402777777781</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G26" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1701,22 +1720,22 @@
         <v>46287.438888888886</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2">
         <v>0.375</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1724,22 +1743,22 @@
         <v>46287.44027777778</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2">
         <v>0.54166666666666663</v>
       </c>
       <c r="G28" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1747,22 +1766,22 @@
         <v>46288.595833333333</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G29" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1770,22 +1789,22 @@
         <v>46288.597916666666</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G30" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1793,22 +1812,22 @@
         <v>46288.606944444444</v>
       </c>
       <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
         <v>69</v>
       </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1816,22 +1835,22 @@
         <v>46288.613194444442</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F32" s="2">
         <v>0.58333333333333337</v>
       </c>
       <c r="G32" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1839,22 +1858,22 @@
         <v>46288.616666666669</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1862,22 +1881,22 @@
         <v>46290.365972222222</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F34" s="2">
         <v>0.33333333333333331</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/area_ismael.xlsx
+++ b/area_ismael.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d9c7f5cb995c5f2/Documentos/ProjetoPython/AfirmaSUS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{A915459A-A95D-4D3A-9069-6AF18F04FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A9631B6-35F9-49DD-A21E-2153DD54EA16}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{A915459A-A95D-4D3A-9069-6AF18F04FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2295FD36-6625-431D-8076-0E741A164955}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B2BFE4F-5340-43B0-ABB5-BC28A4CD0924}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -246,6 +246,135 @@
   </si>
   <si>
     <t>RUA LIBERDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilians </t>
+  </si>
+  <si>
+    <t>ManhÃ£</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JosÃ© francisco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JanduÃ­ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cibelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GraÃ§a </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helena </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarice </t>
+  </si>
+  <si>
+    <t>Sabado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autismo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labirintite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josenildo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aparecida </t>
+  </si>
+  <si>
+    <t>Problemas de coluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnaldo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vania </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saude do idoso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josefa Rita </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manoel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rita </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">joao francisco </t>
+  </si>
+  <si>
+    <t>Wivianne Bezerra da Silva</t>
+  </si>
+  <si>
+    <t>Andriele de Lima Alves</t>
+  </si>
+  <si>
+    <t>USF e saude em geral</t>
+  </si>
+  <si>
+    <t>Roseane Alves da Silva</t>
+  </si>
+  <si>
+    <t>Leandro Pereira de Souza</t>
+  </si>
+  <si>
+    <t>Maria JosÃ© Barbosa da Silva</t>
+  </si>
+  <si>
+    <t>Laiane</t>
+  </si>
+  <si>
+    <t>Mayron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria de socorro </t>
+  </si>
+  <si>
+    <t>Ronaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiviane  Bezerra de Brito </t>
+  </si>
+  <si>
+    <t>RIO TOCANTINS</t>
+  </si>
+  <si>
+    <t>RUA IPIRANGA</t>
+  </si>
+  <si>
+    <t>Saúde do Sono</t>
+  </si>
+  <si>
+    <t>Cuidado Animal</t>
+  </si>
+  <si>
+    <t>Coluna</t>
+  </si>
+  <si>
+    <t>Insegurança Alimentar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressão </t>
   </si>
 </sst>
 </file>
@@ -789,6 +918,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1108,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB1F0A3-556D-4086-8F57-69444587D9FC}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1899,6 +2032,664 @@
         <v>61</v>
       </c>
     </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>46290.623877314814</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>46290.624444444446</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>46290.625763888886</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>46290.626967592594</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>46290.627870370372</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46290.628611111111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>46290.629282407404</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>46290.629328703704</v>
+      </c>
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>46290.630590277775</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>46290.631886574076</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>46290.632118055553</v>
+      </c>
+      <c r="B45" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>46290.635844907411</v>
+      </c>
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46290.637557870374</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46290.639166666668</v>
+      </c>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>46290.639432870368</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46290.63962962963</v>
+      </c>
+      <c r="B50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>46290.641886574071</v>
+      </c>
+      <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>46290.650925925926</v>
+      </c>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>46290.65357638889</v>
+      </c>
+      <c r="B53" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>46293.567245370374</v>
+      </c>
+      <c r="B54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G54" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>46293.567847222221</v>
+      </c>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>46293.577222222222</v>
+      </c>
+      <c r="B56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>46294.341180555559</v>
+      </c>
+      <c r="B57" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>46294.356886574074</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>46294.426932870374</v>
+      </c>
+      <c r="B59" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>46294.432071759256</v>
+      </c>
+      <c r="B60" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>46294.433796296296</v>
+      </c>
+      <c r="B61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>46294.435254629629</v>
+      </c>
+      <c r="B62" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G62" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>46302.629641203705</v>
+      </c>
+      <c r="B63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G63" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
